--- a/user file log.xlsx
+++ b/user file log.xlsx
@@ -1147,7 +1147,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1329,9 +1329,169 @@
         <v>no join configs</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>sales_dataset_100_rows_multi_year.csv</v>
+      </c>
+      <c r="C10" t="str">
+        <v>3/18/2026</v>
+      </c>
+      <c r="D10" t="str">
+        <v>4:34:06 PM</v>
+      </c>
+      <c r="E10" t="str">
+        <v>OrderID, OrderDate, Region, Category, Product, Sales, Quantity, Profit</v>
+      </c>
+      <c r="F10" t="str">
+        <v>no join configs</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>sales_dataset_100_rows_multi_year.csv</v>
+      </c>
+      <c r="C11" t="str">
+        <v>3/18/2026</v>
+      </c>
+      <c r="D11" t="str">
+        <v>4:35:26 PM</v>
+      </c>
+      <c r="E11" t="str">
+        <v>OrderID, OrderDate, Region, Category, Product, Sales, Quantity, Profit</v>
+      </c>
+      <c r="F11" t="str">
+        <v>no join configs</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>sales_dataset_100_rows_multi_year.csv</v>
+      </c>
+      <c r="C12" t="str">
+        <v>3/18/2026</v>
+      </c>
+      <c r="D12" t="str">
+        <v>5:14:40 PM</v>
+      </c>
+      <c r="E12" t="str">
+        <v>OrderID, OrderDate, Region, Category, Product, Sales, Quantity, Profit</v>
+      </c>
+      <c r="F12" t="str">
+        <v>no join configs</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>sales_dataset_100_rows_multi_year.csv</v>
+      </c>
+      <c r="C13" t="str">
+        <v>3/18/2026</v>
+      </c>
+      <c r="D13" t="str">
+        <v>5:18:34 PM</v>
+      </c>
+      <c r="E13" t="str">
+        <v>OrderID, OrderDate, Region, Category, Product, Sales, Quantity, Profit</v>
+      </c>
+      <c r="F13" t="str">
+        <v>no join configs</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>sales_dataset_100_rows_multi_year.csv</v>
+      </c>
+      <c r="C14" t="str">
+        <v>3/18/2026</v>
+      </c>
+      <c r="D14" t="str">
+        <v>7:12:22 PM</v>
+      </c>
+      <c r="E14" t="str">
+        <v>OrderID, OrderDate, Region, Category, Product, Sales, Quantity, Profit</v>
+      </c>
+      <c r="F14" t="str">
+        <v>no join configs</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>sales_dataset_100_rows_multi_year.csv</v>
+      </c>
+      <c r="C15" t="str">
+        <v>3/18/2026</v>
+      </c>
+      <c r="D15" t="str">
+        <v>8:16:21 PM</v>
+      </c>
+      <c r="E15" t="str">
+        <v>OrderID, OrderDate, Region, Category, Product, Sales, Quantity, Profit</v>
+      </c>
+      <c r="F15" t="str">
+        <v>no join configs</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>sales_dataset_100_rows_multi_year.csv</v>
+      </c>
+      <c r="C16" t="str">
+        <v>3/18/2026</v>
+      </c>
+      <c r="D16" t="str">
+        <v>8:18:54 PM</v>
+      </c>
+      <c r="E16" t="str">
+        <v>OrderID, OrderDate, Region, Category, Product, Sales, Quantity, Profit</v>
+      </c>
+      <c r="F16" t="str">
+        <v>no join configs</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>sales_dataset_100_rows_multi_year.csv</v>
+      </c>
+      <c r="C17" t="str">
+        <v>3/18/2026</v>
+      </c>
+      <c r="D17" t="str">
+        <v>9:10:54 PM</v>
+      </c>
+      <c r="E17" t="str">
+        <v>OrderID, OrderDate, Region, Category, Product, Sales, Quantity, Profit</v>
+      </c>
+      <c r="F17" t="str">
+        <v>no join configs</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F17"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/user file log.xlsx
+++ b/user file log.xlsx
@@ -1147,7 +1147,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1489,9 +1489,109 @@
         <v>no join configs</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>sales_dataset_100_rows_multi_year.csv</v>
+      </c>
+      <c r="C18" t="str">
+        <v>3/19/2026</v>
+      </c>
+      <c r="D18" t="str">
+        <v>12:10:38 AM</v>
+      </c>
+      <c r="E18" t="str">
+        <v>OrderID, Region, Category, Product, Sales, Quantity, Profit, OrderDate</v>
+      </c>
+      <c r="F18" t="str">
+        <v>no join configs</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>sales_dataset_100_rows_multi_year.csv</v>
+      </c>
+      <c r="C19" t="str">
+        <v>3/19/2026</v>
+      </c>
+      <c r="D19" t="str">
+        <v>11:14:05 PM</v>
+      </c>
+      <c r="E19" t="str">
+        <v>OrderID, OrderDate, Region, Category, Product, Sales, Quantity, Profit</v>
+      </c>
+      <c r="F19" t="str">
+        <v>no join configs</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>sales_dataset_100_rows_multi_year.csv</v>
+      </c>
+      <c r="C20" t="str">
+        <v>3/20/2026</v>
+      </c>
+      <c r="D20" t="str">
+        <v>12:03:16 AM</v>
+      </c>
+      <c r="E20" t="str">
+        <v>OrderID, OrderDate, Region, Category, Product, Sales, Quantity, Profit</v>
+      </c>
+      <c r="F20" t="str">
+        <v>no join configs</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>sales_dataset_100_rows_multi_year.csv</v>
+      </c>
+      <c r="C21" t="str">
+        <v>3/20/2026</v>
+      </c>
+      <c r="D21" t="str">
+        <v>6:59:30 PM</v>
+      </c>
+      <c r="E21" t="str">
+        <v>OrderID, OrderDate, Region, Category, Product, Sales, Quantity, Profit</v>
+      </c>
+      <c r="F21" t="str">
+        <v>no join configs</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>sales_dataset_100_rows_multi_year.csv</v>
+      </c>
+      <c r="C22" t="str">
+        <v>3/23/2026</v>
+      </c>
+      <c r="D22" t="str">
+        <v>6:36:40 PM</v>
+      </c>
+      <c r="E22" t="str">
+        <v>OrderID, OrderDate, Region, Category, Product, Sales, Quantity, Profit</v>
+      </c>
+      <c r="F22" t="str">
+        <v>no join configs</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F22"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/user file log.xlsx
+++ b/user file log.xlsx
@@ -1147,7 +1147,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F35"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1589,9 +1589,269 @@
         <v>no join configs</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>sales_dataset_100_rows_multi_year.csv</v>
+      </c>
+      <c r="C23" t="str">
+        <v>3/25/2026</v>
+      </c>
+      <c r="D23" t="str">
+        <v>6:43:13 PM</v>
+      </c>
+      <c r="E23" t="str">
+        <v>OrderID, OrderDate, Region, Category, Product, Sales, Quantity, Profit</v>
+      </c>
+      <c r="F23" t="str">
+        <v>no join configs</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>sales_dataset_100_rows_multi_year.csv</v>
+      </c>
+      <c r="C24" t="str">
+        <v>3/25/2026</v>
+      </c>
+      <c r="D24" t="str">
+        <v>6:50:04 PM</v>
+      </c>
+      <c r="E24" t="str">
+        <v>OrderID, OrderDate, Region, Category, Product, Sales, Quantity, Profit</v>
+      </c>
+      <c r="F24" t="str">
+        <v>no join configs</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="str">
+        <v>sales_dataset_100_rows_multi_year.csv</v>
+      </c>
+      <c r="C25" t="str">
+        <v>3/25/2026</v>
+      </c>
+      <c r="D25" t="str">
+        <v>7:27:48 PM</v>
+      </c>
+      <c r="E25" t="str">
+        <v>OrderID, OrderDate, Region, Category, Product, Sales, Quantity, Profit</v>
+      </c>
+      <c r="F25" t="str">
+        <v>no join configs</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="str">
+        <v>sales_dataset_100_rows_multi_year.csv</v>
+      </c>
+      <c r="C26" t="str">
+        <v>3/25/2026</v>
+      </c>
+      <c r="D26" t="str">
+        <v>7:55:57 PM</v>
+      </c>
+      <c r="E26" t="str">
+        <v>OrderID, OrderDate, Region, Category, Product, Sales, Quantity, Profit</v>
+      </c>
+      <c r="F26" t="str">
+        <v>no join configs</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="str">
+        <v>sales_dataset_100_rows_multi_year.csv</v>
+      </c>
+      <c r="C27" t="str">
+        <v>3/25/2026</v>
+      </c>
+      <c r="D27" t="str">
+        <v>8:06:09 PM</v>
+      </c>
+      <c r="E27" t="str">
+        <v>OrderID, OrderDate, Region, Category, Product, Sales, Quantity, Profit</v>
+      </c>
+      <c r="F27" t="str">
+        <v>no join configs</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="str">
+        <v>sales_dataset_100_rows_multi_year.csv</v>
+      </c>
+      <c r="C28" t="str">
+        <v>3/25/2026</v>
+      </c>
+      <c r="D28" t="str">
+        <v>8:08:13 PM</v>
+      </c>
+      <c r="E28" t="str">
+        <v>OrderID, OrderDate, Region, Category, Product, Sales, Quantity, Profit</v>
+      </c>
+      <c r="F28" t="str">
+        <v>no join configs</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="str">
+        <v>sales_dataset_100_rows_multi_year.csv</v>
+      </c>
+      <c r="C29" t="str">
+        <v>3/25/2026</v>
+      </c>
+      <c r="D29" t="str">
+        <v>8:23:11 PM</v>
+      </c>
+      <c r="E29" t="str">
+        <v>OrderID, OrderDate, Region, Category, Product, Sales, Quantity, Profit</v>
+      </c>
+      <c r="F29" t="str">
+        <v>no join configs</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="str">
+        <v>sales_dataset_100_rows_multi_year.csv</v>
+      </c>
+      <c r="C30" t="str">
+        <v>3/25/2026</v>
+      </c>
+      <c r="D30" t="str">
+        <v>8:35:07 PM</v>
+      </c>
+      <c r="E30" t="str">
+        <v>OrderID, OrderDate, Region, Category, Product, Sales, Quantity, Profit</v>
+      </c>
+      <c r="F30" t="str">
+        <v>no join configs</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="str">
+        <v>sales_dataset_100_rows_multi_year.csv</v>
+      </c>
+      <c r="C31" t="str">
+        <v>3/25/2026</v>
+      </c>
+      <c r="D31" t="str">
+        <v>9:01:26 PM</v>
+      </c>
+      <c r="E31" t="str">
+        <v>OrderID, OrderDate, Region, Category, Product, Sales, Quantity, Profit</v>
+      </c>
+      <c r="F31" t="str">
+        <v>no join configs</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="str">
+        <v>sales_dataset_100_rows_multi_year.csv</v>
+      </c>
+      <c r="C32" t="str">
+        <v>3/25/2026</v>
+      </c>
+      <c r="D32" t="str">
+        <v>9:24:21 PM</v>
+      </c>
+      <c r="E32" t="str">
+        <v>OrderID, OrderDate, Region, Category, Product, Sales, Quantity, Profit</v>
+      </c>
+      <c r="F32" t="str">
+        <v>no join configs</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="str">
+        <v>sales_dataset_100_rows_multi_year.csv</v>
+      </c>
+      <c r="C33" t="str">
+        <v>3/25/2026</v>
+      </c>
+      <c r="D33" t="str">
+        <v>9:27:24 PM</v>
+      </c>
+      <c r="E33" t="str">
+        <v>OrderID, OrderDate, Region, Category, Product, Sales, Quantity, Profit</v>
+      </c>
+      <c r="F33" t="str">
+        <v>no join configs</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="str">
+        <v>sales_dataset_100_rows_multi_year.csv</v>
+      </c>
+      <c r="C34" t="str">
+        <v>3/25/2026</v>
+      </c>
+      <c r="D34" t="str">
+        <v>9:28:34 PM</v>
+      </c>
+      <c r="E34" t="str">
+        <v>OrderID, OrderDate, Region, Category, Product, Sales, Quantity, Profit</v>
+      </c>
+      <c r="F34" t="str">
+        <v>no join configs</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="str">
+        <v>sales_dataset_100_rows_multi_year.csv</v>
+      </c>
+      <c r="C35" t="str">
+        <v>3/25/2026</v>
+      </c>
+      <c r="D35" t="str">
+        <v>9:29:33 PM</v>
+      </c>
+      <c r="E35" t="str">
+        <v>OrderID, OrderDate, Region, Category, Product, Sales, Quantity, Profit</v>
+      </c>
+      <c r="F35" t="str">
+        <v>no join configs</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F35"/>
   </ignoredErrors>
 </worksheet>
 </file>